--- a/src/tagueamento/data/regions.template.xlsx
+++ b/src/tagueamento/data/regions.template.xlsx
@@ -606,7 +606,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[EXEMPLO] Internet Banking</t>
+          <t>Internet Banking - Plataforma</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -633,7 +633,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[EXEMPLO] Internet Banking</t>
+          <t>Internet Banking - Plataforma</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -660,7 +660,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[EXEMPLO] Internet Banking</t>
+          <t>Internet Banking - Plataforma</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
